--- a/Data/EC/NIT-9009616838.xlsx
+++ b/Data/EC/NIT-9009616838.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Laura Wilches\Documents\2_ Macro Comfenalco Cartagena\Macro Aviso Incumplimiento y demás\Estados De Cuenta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Operaciones\OneDrive - NIYARAKY COLOMBIA SAS OLD2\Escritorio\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\Estados De Cuenta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B5348537-2BCF-4E9A-85A9-7FA47F5EACF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CD6349C6-CB68-45F8-BA62-853D592067E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{7076F3EC-B343-47FA-AB36-78C656D1FA9C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{646F2939-0C7E-4340-B640-1D9B39E878B5}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -644,22 +644,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>633769</xdr:colOff>
+      <xdr:colOff>717113</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>55950</xdr:rowOff>
+      <xdr:rowOff>75000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>437794</xdr:colOff>
+      <xdr:colOff>435413</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>125025</xdr:rowOff>
+      <xdr:rowOff>115500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Imagen 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DD28CB76-6513-DD0F-E091-BD8F9222BB06}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5F434E28-F6D9-2D05-6036-0E4A2C52B031}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -668,7 +668,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -681,7 +681,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="890944" y="236925"/>
+          <a:off x="964763" y="265500"/>
           <a:ext cx="975600" cy="612000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1010,23 +1010,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2A3C386-A978-4550-8637-AE4E8319CEF0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5587138-87EB-4F56-908D-AEEAB27D820F}">
   <dimension ref="B2:J186"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.59765625" customWidth="1"/>
-    <col min="2" max="2" width="18.9296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="31.46484375" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.73046875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.1328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.59765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.59765625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.265625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.7109375" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="32.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" s="3"/>
       <c r="C2" s="28"/>
       <c r="D2" s="29" t="s">
@@ -1039,7 +1039,7 @@
       <c r="I2" s="29"/>
       <c r="J2" s="29"/>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="28"/>
       <c r="D3" s="30"/>
@@ -1050,7 +1050,7 @@
       <c r="I3" s="30"/>
       <c r="J3" s="30"/>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B4" s="3"/>
       <c r="C4" s="28"/>
       <c r="D4" s="30"/>
@@ -1061,7 +1061,7 @@
       <c r="I4" s="30"/>
       <c r="J4" s="30"/>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" s="3"/>
       <c r="C5" s="28"/>
       <c r="D5" s="31"/>
@@ -1072,8 +1072,8 @@
       <c r="I5" s="31"/>
       <c r="J5" s="31"/>
     </row>
-    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
         <v>70</v>
       </c>
@@ -1088,8 +1088,8 @@
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
     </row>
-    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
         <v>6</v>
       </c>
@@ -1104,8 +1104,8 @@
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
     </row>
-    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
         <v>71</v>
       </c>
@@ -1120,8 +1120,8 @@
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
     </row>
-    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" s="9" t="s">
         <v>72</v>
       </c>
@@ -1140,7 +1140,7 @@
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
         <v>0</v>
       </c>
@@ -1169,7 +1169,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" s="15" t="s">
         <v>8</v>
       </c>
@@ -1192,7 +1192,7 @@
       <c r="I16" s="19"/>
       <c r="J16" s="20"/>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" s="15" t="s">
         <v>8</v>
       </c>
@@ -1215,7 +1215,7 @@
       <c r="I17" s="19"/>
       <c r="J17" s="20"/>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" s="15" t="s">
         <v>8</v>
       </c>
@@ -1238,7 +1238,7 @@
       <c r="I18" s="19"/>
       <c r="J18" s="20"/>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B19" s="15" t="s">
         <v>8</v>
       </c>
@@ -1261,7 +1261,7 @@
       <c r="I19" s="19"/>
       <c r="J19" s="20"/>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B20" s="15" t="s">
         <v>8</v>
       </c>
@@ -1284,7 +1284,7 @@
       <c r="I20" s="19"/>
       <c r="J20" s="20"/>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B21" s="15" t="s">
         <v>8</v>
       </c>
@@ -1307,7 +1307,7 @@
       <c r="I21" s="19"/>
       <c r="J21" s="20"/>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" s="15" t="s">
         <v>8</v>
       </c>
@@ -1330,7 +1330,7 @@
       <c r="I22" s="19"/>
       <c r="J22" s="20"/>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B23" s="15" t="s">
         <v>8</v>
       </c>
@@ -1353,7 +1353,7 @@
       <c r="I23" s="19"/>
       <c r="J23" s="20"/>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B24" s="15" t="s">
         <v>8</v>
       </c>
@@ -1376,7 +1376,7 @@
       <c r="I24" s="19"/>
       <c r="J24" s="20"/>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B25" s="15" t="s">
         <v>8</v>
       </c>
@@ -1399,7 +1399,7 @@
       <c r="I25" s="19"/>
       <c r="J25" s="20"/>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B26" s="15" t="s">
         <v>8</v>
       </c>
@@ -1422,7 +1422,7 @@
       <c r="I26" s="19"/>
       <c r="J26" s="20"/>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B27" s="15" t="s">
         <v>8</v>
       </c>
@@ -1445,7 +1445,7 @@
       <c r="I27" s="19"/>
       <c r="J27" s="20"/>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B28" s="15" t="s">
         <v>8</v>
       </c>
@@ -1468,7 +1468,7 @@
       <c r="I28" s="19"/>
       <c r="J28" s="20"/>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B29" s="15" t="s">
         <v>8</v>
       </c>
@@ -1491,7 +1491,7 @@
       <c r="I29" s="19"/>
       <c r="J29" s="20"/>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B30" s="15" t="s">
         <v>8</v>
       </c>
@@ -1514,7 +1514,7 @@
       <c r="I30" s="19"/>
       <c r="J30" s="20"/>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B31" s="15" t="s">
         <v>8</v>
       </c>
@@ -1537,7 +1537,7 @@
       <c r="I31" s="19"/>
       <c r="J31" s="20"/>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B32" s="15" t="s">
         <v>8</v>
       </c>
@@ -1560,7 +1560,7 @@
       <c r="I32" s="19"/>
       <c r="J32" s="20"/>
     </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B33" s="15" t="s">
         <v>8</v>
       </c>
@@ -1583,7 +1583,7 @@
       <c r="I33" s="19"/>
       <c r="J33" s="20"/>
     </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B34" s="15" t="s">
         <v>8</v>
       </c>
@@ -1606,7 +1606,7 @@
       <c r="I34" s="19"/>
       <c r="J34" s="20"/>
     </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B35" s="15" t="s">
         <v>8</v>
       </c>
@@ -1629,7 +1629,7 @@
       <c r="I35" s="19"/>
       <c r="J35" s="20"/>
     </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B36" s="15" t="s">
         <v>8</v>
       </c>
@@ -1652,7 +1652,7 @@
       <c r="I36" s="19"/>
       <c r="J36" s="20"/>
     </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B37" s="15" t="s">
         <v>8</v>
       </c>
@@ -1675,7 +1675,7 @@
       <c r="I37" s="19"/>
       <c r="J37" s="20"/>
     </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B38" s="15" t="s">
         <v>8</v>
       </c>
@@ -1698,7 +1698,7 @@
       <c r="I38" s="19"/>
       <c r="J38" s="20"/>
     </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B39" s="15" t="s">
         <v>8</v>
       </c>
@@ -1721,7 +1721,7 @@
       <c r="I39" s="19"/>
       <c r="J39" s="20"/>
     </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B40" s="15" t="s">
         <v>8</v>
       </c>
@@ -1744,7 +1744,7 @@
       <c r="I40" s="19"/>
       <c r="J40" s="20"/>
     </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B41" s="15" t="s">
         <v>8</v>
       </c>
@@ -1767,7 +1767,7 @@
       <c r="I41" s="19"/>
       <c r="J41" s="20"/>
     </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B42" s="15" t="s">
         <v>8</v>
       </c>
@@ -1790,7 +1790,7 @@
       <c r="I42" s="19"/>
       <c r="J42" s="20"/>
     </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B43" s="15" t="s">
         <v>8</v>
       </c>
@@ -1813,7 +1813,7 @@
       <c r="I43" s="19"/>
       <c r="J43" s="20"/>
     </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B44" s="15" t="s">
         <v>8</v>
       </c>
@@ -1836,7 +1836,7 @@
       <c r="I44" s="19"/>
       <c r="J44" s="20"/>
     </row>
-    <row r="45" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B45" s="15" t="s">
         <v>8</v>
       </c>
@@ -1859,7 +1859,7 @@
       <c r="I45" s="19"/>
       <c r="J45" s="20"/>
     </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B46" s="15" t="s">
         <v>8</v>
       </c>
@@ -1882,7 +1882,7 @@
       <c r="I46" s="19"/>
       <c r="J46" s="20"/>
     </row>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B47" s="15" t="s">
         <v>8</v>
       </c>
@@ -1905,7 +1905,7 @@
       <c r="I47" s="19"/>
       <c r="J47" s="20"/>
     </row>
-    <row r="48" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B48" s="15" t="s">
         <v>8</v>
       </c>
@@ -1928,7 +1928,7 @@
       <c r="I48" s="19"/>
       <c r="J48" s="20"/>
     </row>
-    <row r="49" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B49" s="15" t="s">
         <v>8</v>
       </c>
@@ -1951,7 +1951,7 @@
       <c r="I49" s="19"/>
       <c r="J49" s="20"/>
     </row>
-    <row r="50" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B50" s="15" t="s">
         <v>8</v>
       </c>
@@ -1974,7 +1974,7 @@
       <c r="I50" s="19"/>
       <c r="J50" s="20"/>
     </row>
-    <row r="51" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B51" s="15" t="s">
         <v>8</v>
       </c>
@@ -1997,7 +1997,7 @@
       <c r="I51" s="19"/>
       <c r="J51" s="20"/>
     </row>
-    <row r="52" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B52" s="15" t="s">
         <v>8</v>
       </c>
@@ -2020,7 +2020,7 @@
       <c r="I52" s="19"/>
       <c r="J52" s="20"/>
     </row>
-    <row r="53" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="53" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B53" s="15" t="s">
         <v>8</v>
       </c>
@@ -2043,7 +2043,7 @@
       <c r="I53" s="19"/>
       <c r="J53" s="20"/>
     </row>
-    <row r="54" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="54" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B54" s="15" t="s">
         <v>8</v>
       </c>
@@ -2066,7 +2066,7 @@
       <c r="I54" s="19"/>
       <c r="J54" s="20"/>
     </row>
-    <row r="55" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="55" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B55" s="15" t="s">
         <v>8</v>
       </c>
@@ -2089,7 +2089,7 @@
       <c r="I55" s="19"/>
       <c r="J55" s="20"/>
     </row>
-    <row r="56" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="56" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B56" s="15" t="s">
         <v>8</v>
       </c>
@@ -2112,7 +2112,7 @@
       <c r="I56" s="19"/>
       <c r="J56" s="20"/>
     </row>
-    <row r="57" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="57" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B57" s="15" t="s">
         <v>8</v>
       </c>
@@ -2135,7 +2135,7 @@
       <c r="I57" s="19"/>
       <c r="J57" s="20"/>
     </row>
-    <row r="58" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="58" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B58" s="15" t="s">
         <v>8</v>
       </c>
@@ -2158,7 +2158,7 @@
       <c r="I58" s="19"/>
       <c r="J58" s="20"/>
     </row>
-    <row r="59" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="59" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B59" s="15" t="s">
         <v>8</v>
       </c>
@@ -2181,7 +2181,7 @@
       <c r="I59" s="19"/>
       <c r="J59" s="20"/>
     </row>
-    <row r="60" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="60" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B60" s="15" t="s">
         <v>8</v>
       </c>
@@ -2204,7 +2204,7 @@
       <c r="I60" s="19"/>
       <c r="J60" s="20"/>
     </row>
-    <row r="61" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="61" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B61" s="15" t="s">
         <v>8</v>
       </c>
@@ -2227,7 +2227,7 @@
       <c r="I61" s="19"/>
       <c r="J61" s="20"/>
     </row>
-    <row r="62" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="62" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B62" s="15" t="s">
         <v>8</v>
       </c>
@@ -2250,7 +2250,7 @@
       <c r="I62" s="19"/>
       <c r="J62" s="20"/>
     </row>
-    <row r="63" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="63" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B63" s="15" t="s">
         <v>8</v>
       </c>
@@ -2273,7 +2273,7 @@
       <c r="I63" s="19"/>
       <c r="J63" s="20"/>
     </row>
-    <row r="64" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="64" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B64" s="15" t="s">
         <v>8</v>
       </c>
@@ -2296,7 +2296,7 @@
       <c r="I64" s="19"/>
       <c r="J64" s="20"/>
     </row>
-    <row r="65" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="65" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B65" s="15" t="s">
         <v>8</v>
       </c>
@@ -2319,7 +2319,7 @@
       <c r="I65" s="19"/>
       <c r="J65" s="20"/>
     </row>
-    <row r="66" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="66" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B66" s="15" t="s">
         <v>8</v>
       </c>
@@ -2342,7 +2342,7 @@
       <c r="I66" s="19"/>
       <c r="J66" s="20"/>
     </row>
-    <row r="67" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="67" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B67" s="15" t="s">
         <v>8</v>
       </c>
@@ -2365,7 +2365,7 @@
       <c r="I67" s="19"/>
       <c r="J67" s="20"/>
     </row>
-    <row r="68" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="68" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B68" s="15" t="s">
         <v>8</v>
       </c>
@@ -2388,7 +2388,7 @@
       <c r="I68" s="19"/>
       <c r="J68" s="20"/>
     </row>
-    <row r="69" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="69" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B69" s="15" t="s">
         <v>8</v>
       </c>
@@ -2411,7 +2411,7 @@
       <c r="I69" s="19"/>
       <c r="J69" s="20"/>
     </row>
-    <row r="70" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="70" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B70" s="15" t="s">
         <v>8</v>
       </c>
@@ -2434,7 +2434,7 @@
       <c r="I70" s="19"/>
       <c r="J70" s="20"/>
     </row>
-    <row r="71" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="71" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B71" s="15" t="s">
         <v>8</v>
       </c>
@@ -2457,7 +2457,7 @@
       <c r="I71" s="19"/>
       <c r="J71" s="20"/>
     </row>
-    <row r="72" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="72" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B72" s="15" t="s">
         <v>8</v>
       </c>
@@ -2480,7 +2480,7 @@
       <c r="I72" s="19"/>
       <c r="J72" s="20"/>
     </row>
-    <row r="73" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="73" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B73" s="15" t="s">
         <v>8</v>
       </c>
@@ -2503,7 +2503,7 @@
       <c r="I73" s="19"/>
       <c r="J73" s="20"/>
     </row>
-    <row r="74" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="74" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B74" s="15" t="s">
         <v>8</v>
       </c>
@@ -2526,7 +2526,7 @@
       <c r="I74" s="19"/>
       <c r="J74" s="20"/>
     </row>
-    <row r="75" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="75" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B75" s="15" t="s">
         <v>8</v>
       </c>
@@ -2549,7 +2549,7 @@
       <c r="I75" s="19"/>
       <c r="J75" s="20"/>
     </row>
-    <row r="76" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="76" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B76" s="15" t="s">
         <v>8</v>
       </c>
@@ -2572,7 +2572,7 @@
       <c r="I76" s="19"/>
       <c r="J76" s="20"/>
     </row>
-    <row r="77" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="77" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B77" s="15" t="s">
         <v>8</v>
       </c>
@@ -2595,7 +2595,7 @@
       <c r="I77" s="19"/>
       <c r="J77" s="20"/>
     </row>
-    <row r="78" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="78" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B78" s="15" t="s">
         <v>8</v>
       </c>
@@ -2618,7 +2618,7 @@
       <c r="I78" s="19"/>
       <c r="J78" s="20"/>
     </row>
-    <row r="79" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="79" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B79" s="15" t="s">
         <v>8</v>
       </c>
@@ -2641,7 +2641,7 @@
       <c r="I79" s="19"/>
       <c r="J79" s="20"/>
     </row>
-    <row r="80" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="80" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B80" s="15" t="s">
         <v>8</v>
       </c>
@@ -2664,7 +2664,7 @@
       <c r="I80" s="19"/>
       <c r="J80" s="20"/>
     </row>
-    <row r="81" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="81" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B81" s="15" t="s">
         <v>8</v>
       </c>
@@ -2687,7 +2687,7 @@
       <c r="I81" s="19"/>
       <c r="J81" s="20"/>
     </row>
-    <row r="82" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="82" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B82" s="15" t="s">
         <v>8</v>
       </c>
@@ -2710,7 +2710,7 @@
       <c r="I82" s="19"/>
       <c r="J82" s="20"/>
     </row>
-    <row r="83" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="83" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B83" s="15" t="s">
         <v>8</v>
       </c>
@@ -2733,7 +2733,7 @@
       <c r="I83" s="19"/>
       <c r="J83" s="20"/>
     </row>
-    <row r="84" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="84" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B84" s="15" t="s">
         <v>8</v>
       </c>
@@ -2756,7 +2756,7 @@
       <c r="I84" s="19"/>
       <c r="J84" s="20"/>
     </row>
-    <row r="85" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="85" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B85" s="15" t="s">
         <v>8</v>
       </c>
@@ -2779,7 +2779,7 @@
       <c r="I85" s="19"/>
       <c r="J85" s="20"/>
     </row>
-    <row r="86" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="86" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B86" s="15" t="s">
         <v>8</v>
       </c>
@@ -2802,7 +2802,7 @@
       <c r="I86" s="19"/>
       <c r="J86" s="20"/>
     </row>
-    <row r="87" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="87" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B87" s="15" t="s">
         <v>8</v>
       </c>
@@ -2825,7 +2825,7 @@
       <c r="I87" s="19"/>
       <c r="J87" s="20"/>
     </row>
-    <row r="88" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="88" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B88" s="15" t="s">
         <v>8</v>
       </c>
@@ -2848,7 +2848,7 @@
       <c r="I88" s="19"/>
       <c r="J88" s="20"/>
     </row>
-    <row r="89" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="89" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B89" s="15" t="s">
         <v>8</v>
       </c>
@@ -2871,7 +2871,7 @@
       <c r="I89" s="19"/>
       <c r="J89" s="20"/>
     </row>
-    <row r="90" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="90" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B90" s="15" t="s">
         <v>8</v>
       </c>
@@ -2894,7 +2894,7 @@
       <c r="I90" s="19"/>
       <c r="J90" s="20"/>
     </row>
-    <row r="91" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="91" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B91" s="15" t="s">
         <v>8</v>
       </c>
@@ -2917,7 +2917,7 @@
       <c r="I91" s="19"/>
       <c r="J91" s="20"/>
     </row>
-    <row r="92" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="92" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B92" s="15" t="s">
         <v>8</v>
       </c>
@@ -2940,7 +2940,7 @@
       <c r="I92" s="19"/>
       <c r="J92" s="20"/>
     </row>
-    <row r="93" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="93" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B93" s="15" t="s">
         <v>8</v>
       </c>
@@ -2963,7 +2963,7 @@
       <c r="I93" s="19"/>
       <c r="J93" s="20"/>
     </row>
-    <row r="94" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="94" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B94" s="15" t="s">
         <v>8</v>
       </c>
@@ -2986,7 +2986,7 @@
       <c r="I94" s="19"/>
       <c r="J94" s="20"/>
     </row>
-    <row r="95" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="95" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B95" s="15" t="s">
         <v>8</v>
       </c>
@@ -3009,7 +3009,7 @@
       <c r="I95" s="19"/>
       <c r="J95" s="20"/>
     </row>
-    <row r="96" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="96" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B96" s="15" t="s">
         <v>8</v>
       </c>
@@ -3032,7 +3032,7 @@
       <c r="I96" s="19"/>
       <c r="J96" s="20"/>
     </row>
-    <row r="97" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="97" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B97" s="15" t="s">
         <v>8</v>
       </c>
@@ -3055,7 +3055,7 @@
       <c r="I97" s="19"/>
       <c r="J97" s="20"/>
     </row>
-    <row r="98" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="98" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B98" s="15" t="s">
         <v>8</v>
       </c>
@@ -3078,7 +3078,7 @@
       <c r="I98" s="19"/>
       <c r="J98" s="20"/>
     </row>
-    <row r="99" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="99" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B99" s="15" t="s">
         <v>8</v>
       </c>
@@ -3101,7 +3101,7 @@
       <c r="I99" s="19"/>
       <c r="J99" s="20"/>
     </row>
-    <row r="100" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="100" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B100" s="15" t="s">
         <v>8</v>
       </c>
@@ -3124,7 +3124,7 @@
       <c r="I100" s="19"/>
       <c r="J100" s="20"/>
     </row>
-    <row r="101" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="101" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B101" s="15" t="s">
         <v>8</v>
       </c>
@@ -3147,7 +3147,7 @@
       <c r="I101" s="19"/>
       <c r="J101" s="20"/>
     </row>
-    <row r="102" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="102" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B102" s="15" t="s">
         <v>8</v>
       </c>
@@ -3170,7 +3170,7 @@
       <c r="I102" s="19"/>
       <c r="J102" s="20"/>
     </row>
-    <row r="103" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="103" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B103" s="15" t="s">
         <v>8</v>
       </c>
@@ -3193,7 +3193,7 @@
       <c r="I103" s="19"/>
       <c r="J103" s="20"/>
     </row>
-    <row r="104" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="104" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B104" s="15" t="s">
         <v>8</v>
       </c>
@@ -3216,7 +3216,7 @@
       <c r="I104" s="19"/>
       <c r="J104" s="20"/>
     </row>
-    <row r="105" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="105" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B105" s="15" t="s">
         <v>8</v>
       </c>
@@ -3239,7 +3239,7 @@
       <c r="I105" s="19"/>
       <c r="J105" s="20"/>
     </row>
-    <row r="106" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="106" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B106" s="15" t="s">
         <v>8</v>
       </c>
@@ -3262,7 +3262,7 @@
       <c r="I106" s="19"/>
       <c r="J106" s="20"/>
     </row>
-    <row r="107" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="107" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B107" s="15" t="s">
         <v>8</v>
       </c>
@@ -3285,7 +3285,7 @@
       <c r="I107" s="19"/>
       <c r="J107" s="20"/>
     </row>
-    <row r="108" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="108" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B108" s="15" t="s">
         <v>8</v>
       </c>
@@ -3308,7 +3308,7 @@
       <c r="I108" s="19"/>
       <c r="J108" s="20"/>
     </row>
-    <row r="109" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="109" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B109" s="15" t="s">
         <v>8</v>
       </c>
@@ -3331,7 +3331,7 @@
       <c r="I109" s="19"/>
       <c r="J109" s="20"/>
     </row>
-    <row r="110" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="110" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B110" s="15" t="s">
         <v>8</v>
       </c>
@@ -3354,7 +3354,7 @@
       <c r="I110" s="19"/>
       <c r="J110" s="20"/>
     </row>
-    <row r="111" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="111" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B111" s="15" t="s">
         <v>8</v>
       </c>
@@ -3377,7 +3377,7 @@
       <c r="I111" s="19"/>
       <c r="J111" s="20"/>
     </row>
-    <row r="112" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="112" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B112" s="15" t="s">
         <v>8</v>
       </c>
@@ -3400,7 +3400,7 @@
       <c r="I112" s="19"/>
       <c r="J112" s="20"/>
     </row>
-    <row r="113" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="113" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B113" s="15" t="s">
         <v>8</v>
       </c>
@@ -3423,7 +3423,7 @@
       <c r="I113" s="19"/>
       <c r="J113" s="20"/>
     </row>
-    <row r="114" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="114" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B114" s="15" t="s">
         <v>8</v>
       </c>
@@ -3446,7 +3446,7 @@
       <c r="I114" s="19"/>
       <c r="J114" s="20"/>
     </row>
-    <row r="115" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="115" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B115" s="15" t="s">
         <v>8</v>
       </c>
@@ -3469,7 +3469,7 @@
       <c r="I115" s="19"/>
       <c r="J115" s="20"/>
     </row>
-    <row r="116" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="116" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B116" s="15" t="s">
         <v>8</v>
       </c>
@@ -3492,7 +3492,7 @@
       <c r="I116" s="19"/>
       <c r="J116" s="20"/>
     </row>
-    <row r="117" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="117" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B117" s="15" t="s">
         <v>8</v>
       </c>
@@ -3515,7 +3515,7 @@
       <c r="I117" s="19"/>
       <c r="J117" s="20"/>
     </row>
-    <row r="118" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="118" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B118" s="15" t="s">
         <v>8</v>
       </c>
@@ -3538,7 +3538,7 @@
       <c r="I118" s="19"/>
       <c r="J118" s="20"/>
     </row>
-    <row r="119" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="119" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B119" s="15" t="s">
         <v>8</v>
       </c>
@@ -3561,7 +3561,7 @@
       <c r="I119" s="19"/>
       <c r="J119" s="20"/>
     </row>
-    <row r="120" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="120" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B120" s="15" t="s">
         <v>8</v>
       </c>
@@ -3584,7 +3584,7 @@
       <c r="I120" s="19"/>
       <c r="J120" s="20"/>
     </row>
-    <row r="121" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="121" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B121" s="15" t="s">
         <v>8</v>
       </c>
@@ -3607,7 +3607,7 @@
       <c r="I121" s="19"/>
       <c r="J121" s="20"/>
     </row>
-    <row r="122" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="122" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B122" s="15" t="s">
         <v>8</v>
       </c>
@@ -3630,7 +3630,7 @@
       <c r="I122" s="19"/>
       <c r="J122" s="20"/>
     </row>
-    <row r="123" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="123" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B123" s="15" t="s">
         <v>8</v>
       </c>
@@ -3653,7 +3653,7 @@
       <c r="I123" s="19"/>
       <c r="J123" s="20"/>
     </row>
-    <row r="124" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="124" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B124" s="15" t="s">
         <v>8</v>
       </c>
@@ -3676,7 +3676,7 @@
       <c r="I124" s="19"/>
       <c r="J124" s="20"/>
     </row>
-    <row r="125" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="125" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B125" s="15" t="s">
         <v>8</v>
       </c>
@@ -3699,7 +3699,7 @@
       <c r="I125" s="19"/>
       <c r="J125" s="20"/>
     </row>
-    <row r="126" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="126" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B126" s="15" t="s">
         <v>8</v>
       </c>
@@ -3722,7 +3722,7 @@
       <c r="I126" s="19"/>
       <c r="J126" s="20"/>
     </row>
-    <row r="127" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="127" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B127" s="15" t="s">
         <v>8</v>
       </c>
@@ -3745,7 +3745,7 @@
       <c r="I127" s="19"/>
       <c r="J127" s="20"/>
     </row>
-    <row r="128" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="128" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B128" s="15" t="s">
         <v>8</v>
       </c>
@@ -3768,7 +3768,7 @@
       <c r="I128" s="19"/>
       <c r="J128" s="20"/>
     </row>
-    <row r="129" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="129" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B129" s="15" t="s">
         <v>8</v>
       </c>
@@ -3791,7 +3791,7 @@
       <c r="I129" s="19"/>
       <c r="J129" s="20"/>
     </row>
-    <row r="130" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="130" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B130" s="15" t="s">
         <v>8</v>
       </c>
@@ -3814,7 +3814,7 @@
       <c r="I130" s="19"/>
       <c r="J130" s="20"/>
     </row>
-    <row r="131" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="131" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B131" s="15" t="s">
         <v>8</v>
       </c>
@@ -3837,7 +3837,7 @@
       <c r="I131" s="19"/>
       <c r="J131" s="20"/>
     </row>
-    <row r="132" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="132" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B132" s="15" t="s">
         <v>8</v>
       </c>
@@ -3860,7 +3860,7 @@
       <c r="I132" s="19"/>
       <c r="J132" s="20"/>
     </row>
-    <row r="133" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="133" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B133" s="15" t="s">
         <v>8</v>
       </c>
@@ -3883,7 +3883,7 @@
       <c r="I133" s="19"/>
       <c r="J133" s="20"/>
     </row>
-    <row r="134" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="134" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B134" s="15" t="s">
         <v>8</v>
       </c>
@@ -3906,7 +3906,7 @@
       <c r="I134" s="19"/>
       <c r="J134" s="20"/>
     </row>
-    <row r="135" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="135" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B135" s="15" t="s">
         <v>8</v>
       </c>
@@ -3929,7 +3929,7 @@
       <c r="I135" s="19"/>
       <c r="J135" s="20"/>
     </row>
-    <row r="136" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="136" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B136" s="15" t="s">
         <v>8</v>
       </c>
@@ -3952,7 +3952,7 @@
       <c r="I136" s="19"/>
       <c r="J136" s="20"/>
     </row>
-    <row r="137" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="137" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B137" s="15" t="s">
         <v>8</v>
       </c>
@@ -3975,7 +3975,7 @@
       <c r="I137" s="19"/>
       <c r="J137" s="20"/>
     </row>
-    <row r="138" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="138" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B138" s="15" t="s">
         <v>8</v>
       </c>
@@ -3998,7 +3998,7 @@
       <c r="I138" s="19"/>
       <c r="J138" s="20"/>
     </row>
-    <row r="139" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="139" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B139" s="15" t="s">
         <v>8</v>
       </c>
@@ -4021,7 +4021,7 @@
       <c r="I139" s="19"/>
       <c r="J139" s="20"/>
     </row>
-    <row r="140" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="140" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B140" s="15" t="s">
         <v>8</v>
       </c>
@@ -4044,7 +4044,7 @@
       <c r="I140" s="19"/>
       <c r="J140" s="20"/>
     </row>
-    <row r="141" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="141" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B141" s="15" t="s">
         <v>8</v>
       </c>
@@ -4067,7 +4067,7 @@
       <c r="I141" s="19"/>
       <c r="J141" s="20"/>
     </row>
-    <row r="142" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="142" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B142" s="15" t="s">
         <v>8</v>
       </c>
@@ -4090,7 +4090,7 @@
       <c r="I142" s="19"/>
       <c r="J142" s="20"/>
     </row>
-    <row r="143" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="143" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B143" s="15" t="s">
         <v>8</v>
       </c>
@@ -4113,7 +4113,7 @@
       <c r="I143" s="19"/>
       <c r="J143" s="20"/>
     </row>
-    <row r="144" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="144" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B144" s="15" t="s">
         <v>8</v>
       </c>
@@ -4136,7 +4136,7 @@
       <c r="I144" s="19"/>
       <c r="J144" s="20"/>
     </row>
-    <row r="145" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="145" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B145" s="15" t="s">
         <v>8</v>
       </c>
@@ -4159,7 +4159,7 @@
       <c r="I145" s="19"/>
       <c r="J145" s="20"/>
     </row>
-    <row r="146" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="146" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B146" s="15" t="s">
         <v>8</v>
       </c>
@@ -4182,7 +4182,7 @@
       <c r="I146" s="19"/>
       <c r="J146" s="20"/>
     </row>
-    <row r="147" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="147" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B147" s="15" t="s">
         <v>8</v>
       </c>
@@ -4205,7 +4205,7 @@
       <c r="I147" s="19"/>
       <c r="J147" s="20"/>
     </row>
-    <row r="148" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="148" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B148" s="15" t="s">
         <v>8</v>
       </c>
@@ -4228,7 +4228,7 @@
       <c r="I148" s="19"/>
       <c r="J148" s="20"/>
     </row>
-    <row r="149" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="149" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B149" s="15" t="s">
         <v>8</v>
       </c>
@@ -4251,7 +4251,7 @@
       <c r="I149" s="19"/>
       <c r="J149" s="20"/>
     </row>
-    <row r="150" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="150" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B150" s="15" t="s">
         <v>8</v>
       </c>
@@ -4274,7 +4274,7 @@
       <c r="I150" s="19"/>
       <c r="J150" s="20"/>
     </row>
-    <row r="151" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="151" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B151" s="15" t="s">
         <v>8</v>
       </c>
@@ -4297,7 +4297,7 @@
       <c r="I151" s="19"/>
       <c r="J151" s="20"/>
     </row>
-    <row r="152" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="152" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B152" s="15" t="s">
         <v>8</v>
       </c>
@@ -4320,7 +4320,7 @@
       <c r="I152" s="19"/>
       <c r="J152" s="20"/>
     </row>
-    <row r="153" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="153" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B153" s="15" t="s">
         <v>8</v>
       </c>
@@ -4343,7 +4343,7 @@
       <c r="I153" s="19"/>
       <c r="J153" s="20"/>
     </row>
-    <row r="154" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="154" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B154" s="15" t="s">
         <v>8</v>
       </c>
@@ -4366,7 +4366,7 @@
       <c r="I154" s="19"/>
       <c r="J154" s="20"/>
     </row>
-    <row r="155" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="155" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B155" s="15" t="s">
         <v>8</v>
       </c>
@@ -4389,7 +4389,7 @@
       <c r="I155" s="19"/>
       <c r="J155" s="20"/>
     </row>
-    <row r="156" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="156" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B156" s="15" t="s">
         <v>8</v>
       </c>
@@ -4412,7 +4412,7 @@
       <c r="I156" s="19"/>
       <c r="J156" s="20"/>
     </row>
-    <row r="157" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="157" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B157" s="15" t="s">
         <v>8</v>
       </c>
@@ -4435,7 +4435,7 @@
       <c r="I157" s="19"/>
       <c r="J157" s="20"/>
     </row>
-    <row r="158" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="158" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B158" s="15" t="s">
         <v>8</v>
       </c>
@@ -4458,7 +4458,7 @@
       <c r="I158" s="19"/>
       <c r="J158" s="20"/>
     </row>
-    <row r="159" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="159" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B159" s="15" t="s">
         <v>8</v>
       </c>
@@ -4481,7 +4481,7 @@
       <c r="I159" s="19"/>
       <c r="J159" s="20"/>
     </row>
-    <row r="160" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="160" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B160" s="15" t="s">
         <v>8</v>
       </c>
@@ -4504,7 +4504,7 @@
       <c r="I160" s="19"/>
       <c r="J160" s="20"/>
     </row>
-    <row r="161" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="161" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B161" s="15" t="s">
         <v>8</v>
       </c>
@@ -4527,7 +4527,7 @@
       <c r="I161" s="19"/>
       <c r="J161" s="20"/>
     </row>
-    <row r="162" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="162" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B162" s="15" t="s">
         <v>8</v>
       </c>
@@ -4550,7 +4550,7 @@
       <c r="I162" s="19"/>
       <c r="J162" s="20"/>
     </row>
-    <row r="163" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="163" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B163" s="15" t="s">
         <v>8</v>
       </c>
@@ -4573,7 +4573,7 @@
       <c r="I163" s="19"/>
       <c r="J163" s="20"/>
     </row>
-    <row r="164" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="164" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B164" s="15" t="s">
         <v>8</v>
       </c>
@@ -4596,7 +4596,7 @@
       <c r="I164" s="19"/>
       <c r="J164" s="20"/>
     </row>
-    <row r="165" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="165" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B165" s="15" t="s">
         <v>8</v>
       </c>
@@ -4619,7 +4619,7 @@
       <c r="I165" s="19"/>
       <c r="J165" s="20"/>
     </row>
-    <row r="166" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="166" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B166" s="15" t="s">
         <v>8</v>
       </c>
@@ -4642,7 +4642,7 @@
       <c r="I166" s="19"/>
       <c r="J166" s="20"/>
     </row>
-    <row r="167" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="167" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B167" s="15" t="s">
         <v>8</v>
       </c>
@@ -4665,7 +4665,7 @@
       <c r="I167" s="19"/>
       <c r="J167" s="20"/>
     </row>
-    <row r="168" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="168" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B168" s="15" t="s">
         <v>8</v>
       </c>
@@ -4688,7 +4688,7 @@
       <c r="I168" s="19"/>
       <c r="J168" s="20"/>
     </row>
-    <row r="169" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="169" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B169" s="15" t="s">
         <v>8</v>
       </c>
@@ -4711,7 +4711,7 @@
       <c r="I169" s="19"/>
       <c r="J169" s="20"/>
     </row>
-    <row r="170" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="170" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B170" s="15" t="s">
         <v>8</v>
       </c>
@@ -4734,7 +4734,7 @@
       <c r="I170" s="19"/>
       <c r="J170" s="20"/>
     </row>
-    <row r="171" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="171" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B171" s="15" t="s">
         <v>8</v>
       </c>
@@ -4757,7 +4757,7 @@
       <c r="I171" s="19"/>
       <c r="J171" s="20"/>
     </row>
-    <row r="172" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="172" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B172" s="15" t="s">
         <v>8</v>
       </c>
@@ -4780,7 +4780,7 @@
       <c r="I172" s="19"/>
       <c r="J172" s="20"/>
     </row>
-    <row r="173" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="173" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B173" s="15" t="s">
         <v>8</v>
       </c>
@@ -4803,7 +4803,7 @@
       <c r="I173" s="19"/>
       <c r="J173" s="20"/>
     </row>
-    <row r="174" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="174" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B174" s="15" t="s">
         <v>8</v>
       </c>
@@ -4826,7 +4826,7 @@
       <c r="I174" s="19"/>
       <c r="J174" s="20"/>
     </row>
-    <row r="175" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="175" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B175" s="15" t="s">
         <v>8</v>
       </c>
@@ -4849,7 +4849,7 @@
       <c r="I175" s="19"/>
       <c r="J175" s="20"/>
     </row>
-    <row r="176" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="176" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B176" s="15" t="s">
         <v>8</v>
       </c>
@@ -4872,7 +4872,7 @@
       <c r="I176" s="19"/>
       <c r="J176" s="20"/>
     </row>
-    <row r="177" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="177" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B177" s="15" t="s">
         <v>8</v>
       </c>
@@ -4895,7 +4895,7 @@
       <c r="I177" s="19"/>
       <c r="J177" s="20"/>
     </row>
-    <row r="178" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="178" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B178" s="15" t="s">
         <v>8</v>
       </c>
@@ -4918,7 +4918,7 @@
       <c r="I178" s="19"/>
       <c r="J178" s="20"/>
     </row>
-    <row r="179" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="179" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B179" s="15" t="s">
         <v>8</v>
       </c>
@@ -4941,7 +4941,7 @@
       <c r="I179" s="19"/>
       <c r="J179" s="20"/>
     </row>
-    <row r="180" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="180" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B180" s="21" t="s">
         <v>8</v>
       </c>
@@ -4964,7 +4964,7 @@
       <c r="I180" s="25"/>
       <c r="J180" s="26"/>
     </row>
-    <row r="185" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="185" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B185" s="32" t="s">
         <v>78</v>
       </c>
@@ -4975,7 +4975,7 @@
       <c r="I185" s="1"/>
       <c r="J185" s="1"/>
     </row>
-    <row r="186" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="186" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B186" s="32" t="s">
         <v>77</v>
       </c>
